--- a/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>AMGN</t>
   </si>
@@ -656,198 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28190000</v>
+      </c>
+      <c r="E8" s="3">
         <v>26323000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25979000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25424000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23362000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23747000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22849000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22991000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21662000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20063000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18676000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17265000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15582000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8415000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6406000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6454000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6159000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4356000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4101000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4069000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4162000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4227000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4422000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3346000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3199000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2708000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19775000</v>
+      </c>
+      <c r="E10" s="3">
         <v>19917000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19525000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19265000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19006000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19646000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18780000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18829000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17435000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15641000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15330000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14066000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12874000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,50 +876,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4755000</v>
+      </c>
+      <c r="E12" s="3">
         <v>4434000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4819000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4207000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4116000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3737000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3562000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3840000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4070000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4297000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4083000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6710000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3167000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -947,51 +963,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E14" s="3">
         <v>489000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1505000</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>47000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>292000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>367000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>105000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>171000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>377000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>298000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>404000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1050000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1022,18 +1044,21 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="N15" s="3">
-        <v>294000</v>
       </c>
       <c r="O15" s="3">
         <v>294000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>294000</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20215000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16679000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18340000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16285000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13688000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13404000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12876000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13197000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13192000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13872000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12809000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11688000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11270000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7975000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9644000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7639000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9139000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9674000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10343000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9973000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9794000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8470000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6191000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5867000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5577000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4312000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,218 +1181,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2755000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-892000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>259000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>256000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>753000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>594000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>928000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>629000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>587000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>455000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>420000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>485000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>448000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14801000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12169000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11296000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12996000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12633000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12883000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12856000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12528000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11165000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8738000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7573000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5820000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2875000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1406000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1197000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1262000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1289000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1392000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1304000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1260000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1079000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1061000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1022000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1053000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>610000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7855000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7346000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6701000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8133000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9138000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9545000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9597000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9163000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7978000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5585000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5265000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5009000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4150000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1138000</v>
+      </c>
+      <c r="E24" s="3">
         <v>794000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>808000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>869000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1296000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1151000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1518000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1441000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1039000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>427000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>184000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>664000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>467000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6717000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6552000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5893000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7264000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7842000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8394000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8079000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7722000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6939000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5158000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5081000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4345000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3683000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6717000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6552000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5893000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7264000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7842000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8394000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8079000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7722000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6939000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5158000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5081000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4345000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3683000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1547,11 +1607,11 @@
       <c r="H29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J29" s="3">
         <v>-6100000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>11</v>
@@ -1568,9 +1628,12 @@
       <c r="O29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2755000</v>
+      </c>
+      <c r="E32" s="3">
         <v>892000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-259000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-256000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-753000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-594000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-928000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-629000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-587000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-455000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-420000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-485000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-448000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6717000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6552000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5893000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7264000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7842000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8394000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1979000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7722000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6939000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5158000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5081000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4345000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3683000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6717000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6552000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5893000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7264000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7842000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8394000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1979000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7722000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6939000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5158000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5081000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4345000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3683000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,386 +1989,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10944000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7629000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7989000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6266000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6037000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6945000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3800000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3241000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4144000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3731000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3805000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3257000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6946000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1676000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>48000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4381000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2874000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22359000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37878000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>34844000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27238000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23295000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15596000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20804000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13695000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6392000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5839000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5324000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4057000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3580000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3237000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3165000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2995000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2546000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2697000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5036000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2896000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9518000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4930000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4086000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3893000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3584000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2940000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2834000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2745000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2435000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2647000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3019000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2744000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2484000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1559000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1423000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1280000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1888000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1794000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1727000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2015000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3409000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2494000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2250000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1886000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1572000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30332000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22186000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19385000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21144000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18440000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37618000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>49476000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46010000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38515000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34713000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27367000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31209000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27593000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E47" s="3">
         <v>249000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>573000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1176000</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3">
         <v>570000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>501000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>443000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>3412000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>400000</v>
       </c>
       <c r="O47" s="3">
         <v>400000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>400000</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6592000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6006000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5750000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5297000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5397000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4958000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4989000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4961000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9814000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5223000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5349000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5326000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5420000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>51270000</v>
+      </c>
+      <c r="E49" s="3">
         <v>31609000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30072000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>31276000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>34116000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22142000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23370000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25030000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26428000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>27481000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28230000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17670000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14334000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,51 +2481,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8709000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5071000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5385000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4055000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1754000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1698000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1549000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1124000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1599000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1592000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1767000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1866000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1124000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2571,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97154000</v>
+      </c>
+      <c r="E54" s="3">
         <v>65121000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>61165000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62948000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>59707000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66416000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>79954000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>77626000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71449000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69009000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66125000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>54298000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48871000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,260 +2657,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1590000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1572000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1366000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1421000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1371000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1207000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1352000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>917000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>965000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1212000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>787000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>905000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>642000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1443000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1591000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>87000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>91000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2953000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4419000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1152000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4403000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2247000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2505000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2495000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>84000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15359000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12524000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10731000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10141000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8511000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7862000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6516000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5884000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9489000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5296000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4655000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9581000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5028000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18392000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15687000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12184000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11653000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12835000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13488000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9020000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11204000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8664000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7008000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7947000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8191000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5754000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>63170000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37354000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33222000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32895000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26950000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29510000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34190000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30193000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29182000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30215000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29623000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24034000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21344000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9360000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8419000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9059000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8991000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10249000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10918000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11503000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6354000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5520000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6008000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6459000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6026000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2744000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3059,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90922000</v>
+      </c>
+      <c r="E66" s="3">
         <v>61460000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54465000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53539000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50034000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53916000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54713000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47751000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43366000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43231000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>44029000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35238000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29842000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3303,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26549000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-28622000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-24600000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-21408000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-21330000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17977000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5072000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-438000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2086000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4624000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7634000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10423000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8919000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3483,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6232000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3661000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6700000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9409000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9673000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12500000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25241000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29875000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28083000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25778000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22096000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19060000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19029000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6717000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6552000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5893000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7264000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7842000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8394000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1979000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7722000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6939000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5158000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5081000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4345000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3683000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3690,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4071000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3417000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3398000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3601000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2206000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1946000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1955000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2105000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2108000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2092000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1286000</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1060000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3957,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8471000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9721000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9261000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10497000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9150000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11296000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11177000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10354000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9731000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8555000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6291000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5882000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5119000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4024,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1112000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-936000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-880000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-608000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-618000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-738000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-664000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-738000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-594000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-718000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-693000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-689000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-567000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4156,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26204000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6044000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>733000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5401000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>5709000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>14339000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4024000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8658000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5547000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5752000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8469000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-786000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,50 +4223,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4556000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-4196000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-4013000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3755000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-3509000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3507000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-3365000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2998000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2396000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1851000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1415000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1118000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-500000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,51 +4400,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21048000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4037000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8271000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4867000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15767000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22490000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6594000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2599000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3771000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2877000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2726000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-674000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4236,55 +4484,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3315000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-360000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1723000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>229000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-908000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3145000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>559000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-903000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>413000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>548000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3689000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3659000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
@@ -973,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>189000</v>
+        <v>42000</v>
       </c>
       <c r="E14" s="3">
         <v>489000</v>
@@ -1079,7 +1079,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20215000</v>
+        <v>20068000</v>
       </c>
       <c r="E17" s="3">
         <v>16679000</v>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7975000</v>
+        <v>8122000</v>
       </c>
       <c r="E18" s="3">
         <v>9644000</v>
@@ -1188,7 +1188,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2755000</v>
+        <v>2608000</v>
       </c>
       <c r="E20" s="3">
         <v>-892000</v>
@@ -1728,7 +1728,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2755000</v>
+        <v>-2608000</v>
       </c>
       <c r="E32" s="3">
         <v>892000</v>

--- a/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>AMGN</t>
   </si>
@@ -973,25 +973,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>42000</v>
+        <v>-1396000</v>
       </c>
       <c r="E14" s="3">
-        <v>489000</v>
+        <v>904000</v>
       </c>
       <c r="F14" s="3">
-        <v>1505000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
+        <v>1979000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>494000</v>
       </c>
       <c r="H14" s="3">
-        <v>47000</v>
+        <v>10000</v>
       </c>
       <c r="I14" s="3">
-        <v>292000</v>
+        <v>573000</v>
       </c>
       <c r="J14" s="3">
-        <v>367000</v>
+        <v>408000</v>
       </c>
       <c r="K14" s="3">
         <v>105000</v>
@@ -1018,25 +1018,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>4071000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3417000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3398000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3601000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2035000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1930000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1904000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1079,25 +1079,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20068000</v>
+        <v>20026000</v>
       </c>
       <c r="E17" s="3">
-        <v>16679000</v>
+        <v>16254000</v>
       </c>
       <c r="F17" s="3">
-        <v>18340000</v>
+        <v>16835000</v>
       </c>
       <c r="G17" s="3">
-        <v>16285000</v>
+        <v>16096000</v>
       </c>
       <c r="H17" s="3">
-        <v>13688000</v>
+        <v>13622000</v>
       </c>
       <c r="I17" s="3">
-        <v>13404000</v>
+        <v>13196000</v>
       </c>
       <c r="J17" s="3">
-        <v>12876000</v>
+        <v>12509000</v>
       </c>
       <c r="K17" s="3">
         <v>13197000</v>
@@ -1124,25 +1124,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8122000</v>
+        <v>8164000</v>
       </c>
       <c r="E18" s="3">
-        <v>9644000</v>
+        <v>10069000</v>
       </c>
       <c r="F18" s="3">
-        <v>7639000</v>
+        <v>9144000</v>
       </c>
       <c r="G18" s="3">
-        <v>9139000</v>
+        <v>9328000</v>
       </c>
       <c r="H18" s="3">
-        <v>9674000</v>
+        <v>9740000</v>
       </c>
       <c r="I18" s="3">
-        <v>10343000</v>
+        <v>10551000</v>
       </c>
       <c r="J18" s="3">
-        <v>9973000</v>
+        <v>10340000</v>
       </c>
       <c r="K18" s="3">
         <v>9794000</v>
@@ -1188,25 +1188,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2608000</v>
+        <v>-1170000</v>
       </c>
       <c r="E20" s="3">
-        <v>-892000</v>
+        <v>413000</v>
       </c>
       <c r="F20" s="3">
-        <v>259000</v>
+        <v>-733000</v>
       </c>
       <c r="G20" s="3">
-        <v>256000</v>
+        <v>-297000</v>
       </c>
       <c r="H20" s="3">
-        <v>753000</v>
+        <v>-697000</v>
       </c>
       <c r="I20" s="3">
-        <v>594000</v>
+        <v>241000</v>
       </c>
       <c r="J20" s="3">
-        <v>928000</v>
+        <v>-573000</v>
       </c>
       <c r="K20" s="3">
         <v>629000</v>
@@ -1233,25 +1233,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14801000</v>
+        <v>13405000</v>
       </c>
       <c r="E21" s="3">
-        <v>12169000</v>
+        <v>13073000</v>
       </c>
       <c r="F21" s="3">
-        <v>11296000</v>
+        <v>13275000</v>
       </c>
       <c r="G21" s="3">
-        <v>12996000</v>
+        <v>13226000</v>
       </c>
       <c r="H21" s="3">
-        <v>12633000</v>
+        <v>12472000</v>
       </c>
       <c r="I21" s="3">
-        <v>12883000</v>
+        <v>12240000</v>
       </c>
       <c r="J21" s="3">
-        <v>12856000</v>
+        <v>12817000</v>
       </c>
       <c r="K21" s="3">
         <v>12528000</v>
@@ -1287,7 +1287,7 @@
         <v>1197000</v>
       </c>
       <c r="G22" s="3">
-        <v>1262000</v>
+        <v>998000</v>
       </c>
       <c r="H22" s="3">
         <v>1289000</v>
@@ -1296,7 +1296,7 @@
         <v>1392000</v>
       </c>
       <c r="J22" s="3">
-        <v>1304000</v>
+        <v>1303000</v>
       </c>
       <c r="K22" s="3">
         <v>1260000</v>
@@ -1386,7 +1386,7 @@
         <v>1151000</v>
       </c>
       <c r="J24" s="3">
-        <v>1518000</v>
+        <v>7618000</v>
       </c>
       <c r="K24" s="3">
         <v>1441000</v>
@@ -1476,7 +1476,7 @@
         <v>8394000</v>
       </c>
       <c r="J26" s="3">
-        <v>8079000</v>
+        <v>1979000</v>
       </c>
       <c r="K26" s="3">
         <v>7722000</v>
@@ -1521,7 +1521,7 @@
         <v>8394000</v>
       </c>
       <c r="J27" s="3">
-        <v>8079000</v>
+        <v>1979000</v>
       </c>
       <c r="K27" s="3">
         <v>7722000</v>
@@ -1592,26 +1592,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>11</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-6100000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>11</v>
@@ -1728,25 +1728,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2608000</v>
+        <v>1170000</v>
       </c>
       <c r="E32" s="3">
-        <v>892000</v>
+        <v>-413000</v>
       </c>
       <c r="F32" s="3">
-        <v>-259000</v>
+        <v>733000</v>
       </c>
       <c r="G32" s="3">
-        <v>-256000</v>
+        <v>297000</v>
       </c>
       <c r="H32" s="3">
-        <v>-753000</v>
+        <v>697000</v>
       </c>
       <c r="I32" s="3">
-        <v>-594000</v>
+        <v>-241000</v>
       </c>
       <c r="J32" s="3">
-        <v>-928000</v>
+        <v>573000</v>
       </c>
       <c r="K32" s="3">
         <v>-629000</v>
@@ -2098,10 +2098,10 @@
         <v>5324000</v>
       </c>
       <c r="H43" s="3">
-        <v>4057000</v>
+        <v>4652000</v>
       </c>
       <c r="I43" s="3">
-        <v>3580000</v>
+        <v>4201000</v>
       </c>
       <c r="J43" s="3">
         <v>3237000</v>
@@ -2176,22 +2176,22 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1928000</v>
+        <v>281000</v>
       </c>
       <c r="E45" s="3">
-        <v>1559000</v>
+        <v>355000</v>
       </c>
       <c r="F45" s="3">
-        <v>1423000</v>
+        <v>200000</v>
       </c>
       <c r="G45" s="3">
-        <v>1280000</v>
+        <v>124000</v>
       </c>
       <c r="H45" s="3">
-        <v>1888000</v>
+        <v>354000</v>
       </c>
       <c r="I45" s="3">
-        <v>1794000</v>
+        <v>266000</v>
       </c>
       <c r="J45" s="3">
         <v>1727000</v>
@@ -2266,25 +2266,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>251000</v>
+        <v>4454000</v>
       </c>
       <c r="E47" s="3">
-        <v>249000</v>
+        <v>3162000</v>
       </c>
       <c r="F47" s="3">
-        <v>573000</v>
+        <v>4503000</v>
       </c>
       <c r="G47" s="3">
-        <v>1176000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>11</v>
+        <v>4076000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>799000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>683000</v>
       </c>
       <c r="J47" s="3">
-        <v>570000</v>
+        <v>1027000</v>
       </c>
       <c r="K47" s="3">
         <v>501000</v>
@@ -2491,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8709000</v>
+        <v>4506000</v>
       </c>
       <c r="E52" s="3">
-        <v>5071000</v>
+        <v>2158000</v>
       </c>
       <c r="F52" s="3">
-        <v>5385000</v>
+        <v>1455000</v>
       </c>
       <c r="G52" s="3">
-        <v>4055000</v>
+        <v>1155000</v>
       </c>
       <c r="H52" s="3">
-        <v>1754000</v>
+        <v>955000</v>
       </c>
       <c r="I52" s="3">
-        <v>1698000</v>
+        <v>1015000</v>
       </c>
       <c r="J52" s="3">
-        <v>1549000</v>
+        <v>1092000</v>
       </c>
       <c r="K52" s="3">
         <v>1124000</v>
@@ -2709,19 +2709,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1443000</v>
+        <v>1562000</v>
       </c>
       <c r="E58" s="3">
-        <v>1591000</v>
+        <v>1747000</v>
       </c>
       <c r="F58" s="3">
-        <v>87000</v>
+        <v>232000</v>
       </c>
       <c r="G58" s="3">
-        <v>91000</v>
+        <v>244000</v>
       </c>
       <c r="H58" s="3">
-        <v>2953000</v>
+        <v>3093000</v>
       </c>
       <c r="I58" s="3">
         <v>4419000</v>
@@ -2754,25 +2754,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15359000</v>
+        <v>2869000</v>
       </c>
       <c r="E59" s="3">
-        <v>12524000</v>
+        <v>2332000</v>
       </c>
       <c r="F59" s="3">
-        <v>10731000</v>
+        <v>2326000</v>
       </c>
       <c r="G59" s="3">
-        <v>10141000</v>
+        <v>2320000</v>
       </c>
       <c r="H59" s="3">
-        <v>8511000</v>
+        <v>2067000</v>
       </c>
       <c r="I59" s="3">
-        <v>7862000</v>
+        <v>1449000</v>
       </c>
       <c r="J59" s="3">
-        <v>6516000</v>
+        <v>1408000</v>
       </c>
       <c r="K59" s="3">
         <v>5884000</v>
@@ -2844,19 +2844,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>63170000</v>
+        <v>63861000</v>
       </c>
       <c r="E61" s="3">
-        <v>37354000</v>
+        <v>37893000</v>
       </c>
       <c r="F61" s="3">
-        <v>33222000</v>
+        <v>33747000</v>
       </c>
       <c r="G61" s="3">
-        <v>32895000</v>
+        <v>33201000</v>
       </c>
       <c r="H61" s="3">
-        <v>26950000</v>
+        <v>27338000</v>
       </c>
       <c r="I61" s="3">
         <v>29510000</v>
@@ -2889,25 +2889,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9360000</v>
+        <v>6315000</v>
       </c>
       <c r="E62" s="3">
-        <v>8419000</v>
+        <v>7869000</v>
       </c>
       <c r="F62" s="3">
-        <v>9059000</v>
+        <v>8534000</v>
       </c>
       <c r="G62" s="3">
-        <v>8991000</v>
+        <v>8685000</v>
       </c>
       <c r="H62" s="3">
-        <v>10249000</v>
+        <v>9861000</v>
       </c>
       <c r="I62" s="3">
-        <v>10918000</v>
+        <v>10054000</v>
       </c>
       <c r="J62" s="3">
-        <v>11503000</v>
+        <v>10337000</v>
       </c>
       <c r="K62" s="3">
         <v>6354000</v>
@@ -3697,25 +3697,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4071000</v>
+        <v>871000</v>
       </c>
       <c r="E83" s="3">
-        <v>3417000</v>
+        <v>817000</v>
       </c>
       <c r="F83" s="3">
-        <v>3398000</v>
+        <v>798000</v>
       </c>
       <c r="G83" s="3">
-        <v>3601000</v>
+        <v>801000</v>
       </c>
       <c r="H83" s="3">
-        <v>2206000</v>
+        <v>635000</v>
       </c>
       <c r="I83" s="3">
-        <v>1946000</v>
+        <v>630000</v>
       </c>
       <c r="J83" s="3">
-        <v>1955000</v>
+        <v>604000</v>
       </c>
       <c r="K83" s="3">
         <v>2105000</v>
@@ -4230,25 +4230,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4556000</v>
+        <v>4556000</v>
       </c>
       <c r="E96" s="3">
-        <v>-4196000</v>
+        <v>4196000</v>
       </c>
       <c r="F96" s="3">
-        <v>-4013000</v>
+        <v>4013000</v>
       </c>
       <c r="G96" s="3">
-        <v>-3755000</v>
+        <v>3755000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3509000</v>
+        <v>3509000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3507000</v>
+        <v>3507000</v>
       </c>
       <c r="J96" s="3">
-        <v>-3365000</v>
+        <v>3365000</v>
       </c>
       <c r="K96" s="3">
         <v>-2998000</v>
@@ -4454,26 +4454,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>AMGN</t>
   </si>
@@ -656,210 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33424000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28190000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26323000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25979000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25424000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23362000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23747000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22849000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22991000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21662000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20063000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18676000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17265000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15582000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8415000</v>
+        <v>10458000</v>
       </c>
       <c r="E9" s="3">
-        <v>6406000</v>
+        <v>7795000</v>
       </c>
       <c r="F9" s="3">
+        <v>6376000</v>
+      </c>
+      <c r="G9" s="3">
         <v>6454000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6159000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4356000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4101000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4069000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4162000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4227000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4422000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3346000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3199000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2708000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>19775000</v>
+        <v>22966000</v>
       </c>
       <c r="E10" s="3">
-        <v>19917000</v>
+        <v>20395000</v>
       </c>
       <c r="F10" s="3">
+        <v>19947000</v>
+      </c>
+      <c r="G10" s="3">
         <v>19525000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19265000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19006000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19646000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18780000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18829000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17435000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15641000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15330000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14066000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12874000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,53 +889,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4755000</v>
+        <v>5964000</v>
       </c>
       <c r="E12" s="3">
+        <v>4784000</v>
+      </c>
+      <c r="F12" s="3">
         <v>4434000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4819000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4207000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4116000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3737000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3562000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3840000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4070000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4297000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4083000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6710000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3167000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,99 +982,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-1396000</v>
+        <v>2349000</v>
       </c>
       <c r="E14" s="3">
-        <v>904000</v>
+        <v>98000</v>
       </c>
       <c r="F14" s="3">
-        <v>1979000</v>
+        <v>933000</v>
       </c>
       <c r="G14" s="3">
+        <v>1986000</v>
+      </c>
+      <c r="H14" s="3">
         <v>494000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>573000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>408000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>105000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>171000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>377000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>298000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>404000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1050000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>4071000</v>
+        <v>5481000</v>
       </c>
       <c r="E15" s="3">
-        <v>3417000</v>
+        <v>3932000</v>
       </c>
       <c r="F15" s="3">
+        <v>3260000</v>
+      </c>
+      <c r="G15" s="3">
         <v>3398000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3601000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2035000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1930000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1904000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="O15" s="3">
-        <v>294000</v>
       </c>
       <c r="P15" s="3">
         <v>294000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>294000</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1073,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20026000</v>
+        <v>23748000</v>
       </c>
       <c r="E17" s="3">
-        <v>16254000</v>
+        <v>18532000</v>
       </c>
       <c r="F17" s="3">
-        <v>16835000</v>
+        <v>16225000</v>
       </c>
       <c r="G17" s="3">
+        <v>16828000</v>
+      </c>
+      <c r="H17" s="3">
         <v>16096000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13622000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13196000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12509000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13197000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13192000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13872000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12809000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11688000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11270000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8164000</v>
+        <v>9676000</v>
       </c>
       <c r="E18" s="3">
-        <v>10069000</v>
+        <v>9658000</v>
       </c>
       <c r="F18" s="3">
-        <v>9144000</v>
+        <v>10098000</v>
       </c>
       <c r="G18" s="3">
+        <v>9151000</v>
+      </c>
+      <c r="H18" s="3">
         <v>9328000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9740000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10551000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10340000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9794000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8470000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6191000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5867000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5577000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4312000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1182,233 +1214,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-437000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1170000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>413000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-733000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-297000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-697000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>241000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-573000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>629000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>587000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>455000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>420000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>485000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>448000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13405000</v>
+        <v>15594000</v>
       </c>
       <c r="E21" s="3">
-        <v>13073000</v>
+        <v>14760000</v>
       </c>
       <c r="F21" s="3">
-        <v>13275000</v>
+        <v>12945000</v>
       </c>
       <c r="G21" s="3">
+        <v>13282000</v>
+      </c>
+      <c r="H21" s="3">
         <v>13226000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12472000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12240000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12817000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12528000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11165000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8738000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7573000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5820000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2875000</v>
+        <v>3665000</v>
       </c>
       <c r="E22" s="3">
-        <v>1406000</v>
+        <v>4075000</v>
       </c>
       <c r="F22" s="3">
-        <v>1197000</v>
+        <v>1533000</v>
       </c>
       <c r="G22" s="3">
+        <v>1208000</v>
+      </c>
+      <c r="H22" s="3">
         <v>998000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1289000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1392000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1303000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1260000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1079000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1061000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1022000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1053000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>610000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4609000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7855000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7346000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6701000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8133000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9138000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9545000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9597000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9163000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7978000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5585000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5265000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5009000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4150000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1138000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>794000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>808000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>869000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1296000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1151000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7618000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1441000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1039000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>427000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>184000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>664000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>467000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1451,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4090000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6717000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6552000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5893000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7264000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7842000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8394000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1979000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7722000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6939000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5158000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5081000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4345000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3683000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4090000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6717000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6552000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5893000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7264000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7842000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8394000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1979000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7722000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6939000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5158000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5081000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4345000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3683000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1586,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>11</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>11</v>
@@ -1631,9 +1691,12 @@
       <c r="P29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1676,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1721,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1170000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-413000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>733000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>297000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>697000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-241000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>573000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-629000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-587000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-455000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-420000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-485000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-448000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4090000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6717000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6552000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5893000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7264000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7842000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8394000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1979000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7722000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6939000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5158000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5081000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4345000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3683000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1856,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4090000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6717000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6552000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5893000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7264000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7842000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8394000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1979000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7722000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6939000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5158000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5081000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4345000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3683000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1990,53 +2075,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11973000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10944000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7629000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7989000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6266000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6037000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6945000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3800000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3241000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4144000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3731000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3805000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3257000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6946000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2044,359 +2133,383 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1676000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4381000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2874000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22359000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37878000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>34844000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27238000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>23295000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15596000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20804000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13695000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7501000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7942000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6392000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5839000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5324000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4652000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4201000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3237000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3165000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2995000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2546000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2697000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5036000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2896000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6998000</v>
+      </c>
+      <c r="E44" s="3">
         <v>9518000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4930000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4086000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3893000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3584000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2940000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2834000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2745000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2435000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2647000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3019000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2744000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2484000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E45" s="3">
         <v>281000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>355000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>124000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>354000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>266000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1727000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2015000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3409000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2494000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2250000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1886000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1572000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29030000</v>
+      </c>
+      <c r="E46" s="3">
         <v>30332000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22186000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19385000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21144000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18440000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37618000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49476000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46010000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38515000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34713000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27367000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31209000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27593000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4454000</v>
+        <v>4770000</v>
       </c>
       <c r="E47" s="3">
+        <v>5057000</v>
+      </c>
+      <c r="F47" s="3">
         <v>3162000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4503000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4076000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>799000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>683000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1027000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>501000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>443000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>3412000</v>
-      </c>
-      <c r="O47" s="3">
-        <v>400000</v>
       </c>
       <c r="P47" s="3">
         <v>400000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>400000</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7100000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6592000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6006000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5750000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5297000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5397000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4958000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4989000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4961000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9814000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5223000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5349000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5326000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5420000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>46336000</v>
+      </c>
+      <c r="E49" s="3">
         <v>51270000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>31609000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>30072000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>31276000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>34116000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22142000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23370000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25030000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26428000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27481000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28230000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17670000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14334000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2439,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2484,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4506000</v>
+        <v>4603000</v>
       </c>
       <c r="E52" s="3">
+        <v>3903000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2158000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1455000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1155000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>955000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1015000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1092000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1124000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1599000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1592000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1767000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1866000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1124000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2574,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>91839000</v>
+      </c>
+      <c r="E54" s="3">
         <v>97154000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65121000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>61165000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62948000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>59707000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66416000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79954000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77626000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71449000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69009000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66125000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54298000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>48871000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2639,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2658,278 +2787,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1908000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1590000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1572000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1366000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1421000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1371000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1207000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1352000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>917000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>965000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1212000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>787000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>905000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>642000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3657000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1562000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1747000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>232000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>244000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3093000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4419000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1152000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4403000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2247000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>500000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2505000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2495000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>84000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3861000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2869000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2332000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2326000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2320000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2067000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1449000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1408000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5884000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9489000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5296000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4655000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9581000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5028000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23099000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18392000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15687000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12184000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11653000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12835000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13488000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9020000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11204000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8664000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7008000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7947000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8191000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5754000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57222000</v>
+      </c>
+      <c r="E61" s="3">
         <v>63861000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37893000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33747000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33201000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27338000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29510000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>34190000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30193000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29182000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30215000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29623000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24034000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21344000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4025000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6315000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7869000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8534000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8685000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9861000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10054000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10337000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6354000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5520000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6008000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6459000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6026000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2744000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2972,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3017,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3062,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85962000</v>
+      </c>
+      <c r="E66" s="3">
         <v>90922000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61460000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54465000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53539000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50034000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53916000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54713000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47751000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43366000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43231000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>44029000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>35238000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29842000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3127,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3171,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3216,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3261,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3306,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-27590000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-26549000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28622000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-24600000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-21408000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-21330000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17977000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5072000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-438000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2086000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4624000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7634000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10423000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8919000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3396,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3441,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3486,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5877000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6232000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3661000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6700000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9409000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9673000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12500000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25241000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29875000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28083000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25778000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22096000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19060000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19029000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4090000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6717000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6552000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5893000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7264000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7842000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8394000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1979000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7722000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6939000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5158000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5081000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4345000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3683000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3691,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>792000</v>
+      </c>
+      <c r="E83" s="3">
         <v>871000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>817000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>798000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>801000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>635000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>630000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>604000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2105000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2108000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2092000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1286000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1060000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3780,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3825,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3915,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3960,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11490000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8471000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9721000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9261000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10497000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9150000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11296000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11177000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10354000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9731000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8555000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6291000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5882000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5119000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4025,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1096000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1112000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-936000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-880000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-608000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-618000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-738000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-664000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-738000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-594000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-718000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-693000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-689000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-567000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4114,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4159,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1046000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26204000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6044000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>733000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5401000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5709000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14339000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4024000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8658000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5547000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5752000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8469000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-786000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4224,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4832000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4556000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4196000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4013000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3755000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3509000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3507000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3365000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2998000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2396000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1851000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1415000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1118000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-500000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4313,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4358,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4403,54 +4645,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9415000</v>
+      </c>
+      <c r="E100" s="3">
         <v>21048000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4037000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8271000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4867000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15767000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22490000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6594000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2599000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3771000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2877000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2726000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-674000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4475,8 +4723,8 @@
       <c r="J101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4487,58 +4735,64 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1029000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3315000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-360000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1723000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>229000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-908000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3145000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>559000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-903000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>413000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-74000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>548000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3689000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3659000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>AMGN</t>
   </si>
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36751000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33424000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28190000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26323000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25979000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25424000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23362000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23747000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22849000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22991000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21662000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20063000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18676000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17265000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15582000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10737000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10458000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7795000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6376000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6454000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6159000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4356000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4101000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4069000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4162000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4227000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4422000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3346000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3199000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2708000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>26014000</v>
+      </c>
+      <c r="E10" s="3">
         <v>22966000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20395000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19947000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19525000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19265000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19006000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19646000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18780000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18829000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17435000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15641000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15330000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14066000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12874000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,56 +902,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>7272000</v>
+      </c>
+      <c r="E12" s="3">
         <v>5964000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4784000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4434000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4819000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4207000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4116000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3737000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3562000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3840000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4070000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4297000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4083000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6710000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3167000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,105 +1001,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2349000</v>
       </c>
-      <c r="E14" s="3">
-        <v>98000</v>
-      </c>
       <c r="F14" s="3">
+        <v>263000</v>
+      </c>
+      <c r="G14" s="3">
         <v>933000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1986000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>494000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>573000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>408000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>105000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>171000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>377000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>298000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>404000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1050000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>5043000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5481000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3932000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3260000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3398000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3601000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2035000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1930000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1904000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="P15" s="3">
-        <v>294000</v>
       </c>
       <c r="Q15" s="3">
         <v>294000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>294000</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25177000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23748000</v>
       </c>
-      <c r="E17" s="3">
-        <v>18532000</v>
-      </c>
       <c r="F17" s="3">
+        <v>18367000</v>
+      </c>
+      <c r="G17" s="3">
         <v>16225000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16828000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16096000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13622000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13196000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12509000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13197000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13192000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13872000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12809000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11688000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11270000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11574000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9676000</v>
       </c>
-      <c r="E18" s="3">
-        <v>9658000</v>
-      </c>
       <c r="F18" s="3">
+        <v>9823000</v>
+      </c>
+      <c r="G18" s="3">
         <v>10098000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9151000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9328000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9740000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10551000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10340000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9794000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8470000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6191000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5867000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5577000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4312000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,248 +1247,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-399000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-437000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1170000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>413000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-733000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-297000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-697000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>241000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-573000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>629000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>587000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>455000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>420000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>485000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>448000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17016000</v>
+      </c>
+      <c r="E21" s="3">
         <v>15594000</v>
       </c>
-      <c r="E21" s="3">
-        <v>14760000</v>
-      </c>
       <c r="F21" s="3">
+        <v>14925000</v>
+      </c>
+      <c r="G21" s="3">
         <v>12945000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13282000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13226000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12472000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12240000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12817000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12528000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11165000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8738000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7573000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5820000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3163000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3665000</v>
       </c>
-      <c r="E22" s="3">
-        <v>4075000</v>
-      </c>
       <c r="F22" s="3">
+        <v>4100000</v>
+      </c>
+      <c r="G22" s="3">
         <v>1533000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1208000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>998000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1289000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1392000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1303000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1260000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1079000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1061000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1022000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1053000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>610000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8976000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4609000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7855000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7346000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6701000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8133000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9138000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9545000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9597000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9163000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7978000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5585000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5265000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5009000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4150000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="E24" s="3">
         <v>519000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1138000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>794000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>808000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>869000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1296000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1151000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7618000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1441000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1039000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>427000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>184000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>664000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>467000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7711000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4090000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6717000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6552000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5893000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7264000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7842000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8394000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1979000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7722000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6939000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5158000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5081000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4345000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3683000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7711000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4090000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6717000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6552000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5893000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7264000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7842000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8394000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1979000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7722000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6939000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5158000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5081000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4345000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3683000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,8 +1736,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>11</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>11</v>
@@ -1694,9 +1754,12 @@
       <c r="Q29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E32" s="3">
         <v>437000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1170000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-413000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>733000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>297000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>697000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-241000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>573000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-629000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-587000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-455000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-420000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-485000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-448000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7711000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4090000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6717000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6552000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5893000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7264000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7842000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8394000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1979000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7722000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6939000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5158000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5081000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4345000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3683000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7711000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4090000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6717000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6552000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5893000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7264000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7842000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8394000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1979000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7722000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6939000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5158000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5081000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4345000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3683000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,56 +2161,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9129000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11973000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10944000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7629000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7989000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6266000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6037000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6945000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3800000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3241000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4144000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3731000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3805000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3257000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6946000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2136,380 +2225,404 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1676000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>48000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4381000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2874000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22359000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37878000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>34844000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27238000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>23295000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15596000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20804000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13695000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7501000</v>
+        <v>9570000</v>
       </c>
       <c r="E43" s="3">
+        <v>6782000</v>
+      </c>
+      <c r="F43" s="3">
         <v>7942000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6392000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5839000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5324000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4652000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4201000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3237000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3165000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2995000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2546000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2697000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5036000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2896000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6225000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6998000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9518000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4930000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4086000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3893000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3584000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2940000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2834000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2745000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2435000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2647000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3019000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2744000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2484000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>419000</v>
+        <v>1188000</v>
       </c>
       <c r="E45" s="3">
+        <v>1138000</v>
+      </c>
+      <c r="F45" s="3">
         <v>281000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>355000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>124000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>354000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>266000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1727000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2015000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3409000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2494000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2250000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1886000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1572000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29057000</v>
+      </c>
+      <c r="E46" s="3">
         <v>29030000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30332000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22186000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19385000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21144000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18440000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37618000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49476000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>46010000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38515000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>34713000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27367000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31209000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>27593000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6804000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4770000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5057000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3162000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4503000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4076000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>799000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>683000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1027000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>501000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>443000</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>3412000</v>
-      </c>
-      <c r="P47" s="3">
-        <v>400000</v>
       </c>
       <c r="Q47" s="3">
         <v>400000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>400000</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8515000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7100000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6592000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6006000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5750000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5297000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5397000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4958000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4989000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4961000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9814000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5223000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5349000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5326000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5420000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>40956000</v>
+      </c>
+      <c r="E49" s="3">
         <v>46336000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>51270000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>31609000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>30072000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>31276000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>34116000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22142000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23370000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25030000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26428000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>27481000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28230000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17670000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14334000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5254000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4603000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3903000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2158000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1455000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1155000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>955000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1015000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1092000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1124000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1599000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1592000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1767000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1866000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1124000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>90586000</v>
+      </c>
+      <c r="E54" s="3">
         <v>91839000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>97154000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>65121000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61165000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62948000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>59707000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66416000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79954000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77626000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71449000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69009000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66125000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54298000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>48871000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,296 +2917,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2367000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1908000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1590000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1572000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1366000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1421000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1371000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1207000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1352000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>917000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>965000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1212000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>787000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>905000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>642000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4734000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3657000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1562000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1747000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>232000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>244000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3093000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4419000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1152000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4403000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2247000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>500000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2505000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2495000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>84000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3861000</v>
+        <v>12343000</v>
       </c>
       <c r="E59" s="3">
-        <v>2869000</v>
+        <v>12266000</v>
       </c>
       <c r="F59" s="3">
-        <v>2332000</v>
+        <v>10140000</v>
       </c>
       <c r="G59" s="3">
+        <v>8318000</v>
+      </c>
+      <c r="H59" s="3">
         <v>2326000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2320000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2067000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1449000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1408000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5884000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9489000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5296000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4655000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9581000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5028000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25489000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23099000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18392000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15687000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12184000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11653000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12835000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13488000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9020000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11204000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8664000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7008000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7947000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8191000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5754000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>50701000</v>
+      </c>
+      <c r="E61" s="3">
         <v>57222000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>63861000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37893000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33747000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33201000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27338000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29510000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>34190000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30193000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29182000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30215000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29623000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24034000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21344000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4372000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4025000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6315000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7869000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8534000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8685000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9861000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10054000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10337000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6354000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5520000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6008000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6459000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6026000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2744000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>81928000</v>
+      </c>
+      <c r="E66" s="3">
         <v>85962000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90922000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61460000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54465000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53539000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50034000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53916000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54713000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47751000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43366000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43231000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>44029000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35238000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29842000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25107000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27590000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-26549000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28622000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-24600000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-21408000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-21330000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17977000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5072000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-438000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2086000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4624000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7634000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10423000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8919000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8658000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5877000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6232000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3661000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6700000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9409000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9673000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12500000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25241000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29875000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28083000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25778000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22096000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19060000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19029000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7711000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4090000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6717000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6552000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5893000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7264000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7842000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8394000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1979000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7722000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6939000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5158000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5081000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4345000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3683000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E83" s="3">
         <v>792000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>871000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>817000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>798000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>801000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>635000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>630000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>604000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2105000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2108000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2092000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1286000</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1060000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9958000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11490000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8471000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9721000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9261000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10497000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9150000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11296000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11177000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10354000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9731000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8555000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6291000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5882000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5119000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1858000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1096000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1112000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-936000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-880000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-608000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-618000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-738000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-664000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-738000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-594000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-718000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-693000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-689000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-567000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1943000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1046000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26204000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6044000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>733000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5401000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5709000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14339000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4024000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8658000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5547000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5752000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8469000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-786000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5124000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4832000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4556000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4196000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4013000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3755000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3509000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3507000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3365000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2998000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2396000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1851000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1415000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1118000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-500000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,57 +4890,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10859000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9415000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21048000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4037000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8271000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4867000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15767000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22490000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6594000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2599000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3771000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2877000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2726000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-674000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4726,8 +4974,8 @@
       <c r="K101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4738,61 +4986,67 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2844000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1029000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3315000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-360000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1723000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>229000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-908000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3145000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>559000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-903000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>413000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-74000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>548000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3689000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3659000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
